--- a/education_surveys/026_digital_vs_print_reader_preferences_questionnaire--education_surveys.xlsx
+++ b/education_surveys/026_digital_vs_print_reader_preferences_questionnaire--education_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -873,8 +873,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -902,12 +902,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'digital_only'}</t>
+          <t>digital_only</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Digital Only'}</t>
+          <t>Digital Only</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'print_only'}</t>
+          <t>print_only</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Print Only'}</t>
+          <t>Print Only</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'e-reader'}</t>
+          <t>e-reader</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'E-Reader'}</t>
+          <t>E-Reader</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'tablet'}</t>
+          <t>tablet</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Tablet'}</t>
+          <t>Tablet</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'smartphone'}</t>
+          <t>smartphone</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Smartphone'}</t>
+          <t>Smartphone</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'home'}</t>
+          <t>home</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Home'}</t>
+          <t>Home</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'office'}</t>
+          <t>office</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Office'}</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -1174,12 +1174,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'public_transportation'}</t>
+          <t>public_transportation</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Public Transportation'}</t>
+          <t>Public Transportation</t>
         </is>
       </c>
     </row>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'less_than_15_minutes'}</t>
+          <t>less_than_15_minutes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Less than 15 minutes'}</t>
+          <t>Less than 15 minutes</t>
         </is>
       </c>
     </row>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'15-30_minutes'}</t>
+          <t>15-30_minutes</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': '15-30 minutes'}</t>
+          <t>15-30 minutes</t>
         </is>
       </c>
     </row>
@@ -1242,12 +1242,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'30-60_minutes'}</t>
+          <t>30-60_minutes</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': '30-60 minutes'}</t>
+          <t>30-60 minutes</t>
         </is>
       </c>
     </row>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'more_than_1_hour'}</t>
+          <t>more_than_1_hour</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'More than 1 hour'}</t>
+          <t>More than 1 hour</t>
         </is>
       </c>
     </row>
@@ -1276,12 +1276,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'digital'}</t>
+          <t>digital</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Digital'}</t>
+          <t>Digital</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'print'}</t>
+          <t>print</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Print'}</t>
+          <t>Print</t>
         </is>
       </c>
     </row>
@@ -1310,12 +1310,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'digital_only'}</t>
+          <t>digital_only</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'Digital Only'}</t>
+          <t>Digital Only</t>
         </is>
       </c>
     </row>
@@ -1327,12 +1327,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'print_only'}</t>
+          <t>print_only</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'Print Only'}</t>
+          <t>Print Only</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1361,12 +1361,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'digital_only'}</t>
+          <t>digital_only</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'Digital Only'}</t>
+          <t>Digital Only</t>
         </is>
       </c>
     </row>
@@ -1378,12 +1378,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'print_only'}</t>
+          <t>print_only</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'Print Only'}</t>
+          <t>Print Only</t>
         </is>
       </c>
     </row>
@@ -1395,12 +1395,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'digital_only'}</t>
+          <t>digital_only</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'Digital Only'}</t>
+          <t>Digital Only</t>
         </is>
       </c>
     </row>
@@ -1429,12 +1429,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_'print_only'}</t>
+          <t>print_only</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 'Print Only'}</t>
+          <t>Print Only</t>
         </is>
       </c>
     </row>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1463,12 +1463,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_'digital_only'}</t>
+          <t>digital_only</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': 'Digital Only'}</t>
+          <t>Digital Only</t>
         </is>
       </c>
     </row>
@@ -1480,12 +1480,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'value':_'print_only'}</t>
+          <t>print_only</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'value': 'Print Only'}</t>
+          <t>Print Only</t>
         </is>
       </c>
     </row>
@@ -1497,12 +1497,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'value': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
